--- a/ceshi.xlsx
+++ b/ceshi.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20160" windowHeight="8844"/>
+    <workbookView windowWidth="19308" windowHeight="8844"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$G$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$G$176</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="400">
   <si>
     <t>名称</t>
   </si>
@@ -612,6 +612,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Statista</t>
     </r>
     <r>
@@ -644,6 +650,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Statista</t>
     </r>
     <r>
@@ -1027,16 +1039,45 @@
     <t>《少儿多媒体图书馆》资源分为幼教、绘本、绘本导读、语文、数学、英语、舞蹈、音乐、美术、百科、科学探索、诗词、国学等多个方向。主要分为绘声绘色、国学文化、科普百科、艺术培养、中小课堂、益智互动、家校共育几大模块，侧重于关注少儿的兴趣培养、成长教育以及家校共育，打造快乐型、自主型、互动型的学习平台。</t>
   </si>
   <si>
-    <t>书同文古籍数据库/《十通》</t>
+    <t>书同文古籍数据库/十通</t>
   </si>
   <si>
     <t>中国历代典章制度的大型工具书，由十部书名中带有"通"字的古典文献组成。</t>
   </si>
   <si>
-    <t>书同文古籍数据库/《四部丛刊》</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书同文古籍数据库</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四部丛刊</t>
+    </r>
   </si>
   <si>
     <t>该书电子版底本采用北京大学图书馆善本部馆藏上海涵芬楼景印《四部丛刊》。</t>
+  </si>
+  <si>
+    <t>书同文古籍数据库/四部丛刊</t>
   </si>
   <si>
     <t>书同文古籍数据库/清会典</t>
@@ -1222,7 +1263,7 @@
     <t>“中国历史人物传记资源库”由国家图书馆出版社与北京大学数据分析研究中心联合研制。该库为大型历史人物传记文献资料库。</t>
   </si>
   <si>
-    <t>中国人民大学复印报刊资料库</t>
+    <t>人大复印报刊资料数据库</t>
   </si>
   <si>
     <t>该资源囊括了人文社会科学领域的各个学科，内容源于“复印报刊资料”系列纸质期刊，是由专业编辑和学界专家依循严谨的学术标准对海量学术信息进行精选整理、分类编辑，最终形成优中选优的精品成果库。我馆已订购自2014年至今出版内容，提供【全文数据库】和【数字期刊库】两个模块使用服务。</t>
@@ -1312,7 +1353,7 @@
     <t>中国知网/中国重要会议论文全文数据库清华同方</t>
   </si>
   <si>
-    <t>中国资讯行（infobank）</t>
+    <t>中国资讯行</t>
   </si>
   <si>
     <t>收录了从中央到地方1000多种综合性财经类主流媒体，包括报纸、杂志、学报、书籍和各类年鉴，以及海外综合类、财经类报纸，政府或民间专业信息机构的宏观经济分析或行业报告，反映了全国各地区、各行业的经济动态。</t>
@@ -1328,6 +1369,125 @@
   </si>
   <si>
     <t>“中文社会科学引文索引数据库”由南京大学中国社会科学研究评价中心开发研制，用于检索中文人文社会科学领域的论文收录和被引用情况。</t>
+  </si>
+  <si>
+    <t>中华经典古籍库</t>
+  </si>
+  <si>
+    <t>《中华经典古籍库》是大型古籍整理本数据库，收录了中华书局及其他古籍出版社正式出版的整理本古籍图书，提供便捷的阅读、查询、文献征引等服务。第一到三期数据资源主要为中华书局出版的整理本古籍，从第四期开始收录合作出版社的优质资源。合作对象包括巴蜀书社、凤凰出版社、广陵书社、天津古籍出版社、岳麓书社、浙江古籍出版社等20余家出版机构。资源涵盖经、史、子、集各部，包含二十四史、通鉴、新编诸子集成、十三经清人注疏、史料笔记丛刊、古典文学基本丛书、佛教典籍选刊等经典系列，资源保留了图书完整的前言、注释、校勘等整理成果。</t>
+  </si>
+  <si>
+    <t>网络/镜像（待安装）</t>
+  </si>
+  <si>
+    <t>万方数据/中国法律法规数据库</t>
+  </si>
+  <si>
+    <t>中国法律法规数据库（ China Laws &amp; Regulations Database），收录始于1949年，涵盖国家法律法规、行政法规、地方法规、国际条约及惯例、司法解释、合同范本等，权威、专业。每月更新，年新增量不低于8万条。</t>
+  </si>
+  <si>
+    <t>中华医学期刊全文数据库</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国知网</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国专利全文数据库</t>
+    </r>
+  </si>
+  <si>
+    <t>完整收录并动态更新中国大陆历年专利文献的大型专利图文数据库，与国家知识产权局知识产权出版社合作建设，内容全面、权威、实用，也是专注于科技研究、科技产出整合关联的专利数据库。</t>
+  </si>
+  <si>
+    <t>中国知网/中国专利全文数据库清华同方</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国知网</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国图书全文数据库（心可书馆）</t>
+    </r>
+  </si>
+  <si>
+    <t>《中国图书全文数据库（心可书馆）》已收录精品专业图书超过9万余本，资源覆盖人文社科、自然科学、工程技术等各领域，并通过参考文献、引证文献等关联关系，实现了图书内容与其它各类文献的深度关联融合。
+WEB版试用期：即日起至2026年12月31日。</t>
+  </si>
+  <si>
+    <t>中国知网/中国图书全文数据库（心可书馆）清华同方</t>
+  </si>
+  <si>
+    <t>中华古籍书目数据库</t>
+  </si>
+  <si>
+    <t>书目</t>
+  </si>
+  <si>
+    <t>该库将自古至今已整理点校的各类书目资源进行数字碎片化处理，在确保数据准确、权威的前提下，统一呈现，实现一站式检索的平台。数据库共收录305种资源，88万余条目，共计14840余万字。其中一期收录65种图书，58万余条书目，6797余万字；二期收录53种图书，30万余条书目，3400余万字。三期收录图书187种，4643余万字。数据保留了原书正文的全部内容，包括提要、注释、子目、图片乃至专名线、书名线等信息，并在显示上做了差异化处理。</t>
+  </si>
+  <si>
+    <t>Web of Science/SCIE</t>
+  </si>
+  <si>
+    <t>科学引文索引数据库（Science Citation Index Expanded，简称SCIE）是Web of Science核心合集的核心数据库，是全球权威的自然科学引文数据库。它收录了自然科学领域9400多种国际性、高影响力的学术期刊，数据最早可回溯到1900年，涵盖了178个学科领域。我馆可访问2000年以来的数据。</t>
+  </si>
+  <si>
+    <t>万方中国旧方志全文数据库</t>
+  </si>
+  <si>
+    <t>《中国旧方志全文数据库》的内容由北京万方数据股份有限公司对已收藏的旧方志数据归种整理,经过认真对比去重,精心筛迭部分旧志进行文本识别,形成旧志可全文检索,可图文对照阅读,更便于读者查阅参考。</t>
+  </si>
+  <si>
+    <t>中国大百科全书数据库（第一版及第二版）</t>
+  </si>
+  <si>
+    <t>1978年，国务院决定编纂出版《中国大百科全书》。《中国大百科全书》第一版按学科或知识门类分卷编纂，1993年出齐。全书以条目形式全面、系统、准确地介绍科学知识和基本事实，内容包括哲学、社会科学、文学艺术、文化教育、自然科学、工程技术等66个学科和知识领域。总计为74卷(含总索引卷)，选收条目77859个，总字数12568万字，并附有49765幅随文图。《中国大百科全书》第一版的出版结束了中国没有百科全书的历史。 《中国大百科全书》第二版从1996年开始修订重编，2009年出版。第二版按条目标题的汉语拼音字母顺序统一编排，使读者更加便于寻检查阅。第二版共32卷，其中正文30卷，索引、附录2卷，每卷约180万字，共选收6万个条日，总字数6000万字，配图3万幅，其中地图干余幅。全书精装全彩印刷。第二版是按国际惯例编纂的大型现代综合性百科全书。</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1670,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1526,6 +1686,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1861,7 +2027,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1885,16 +2051,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1903,89 +2069,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1994,6 +2160,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2065,7 +2237,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2379,14 +2551,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="6"/>
+  <dimension ref="A1:G176"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="15.6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="30.8" customWidth="1"/>
-    <col min="2" max="2" width="13.6" customWidth="1"/>
-    <col min="4" max="4" width="65.7" customWidth="1"/>
-    <col min="5" max="5" width="13.3" customWidth="1"/>
-    <col min="7" max="7" width="44.9" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="2" max="2" width="14.2" customWidth="1"/>
+    <col min="3" max="3" width="13.9" customWidth="1"/>
+    <col min="4" max="4" width="47.2" customWidth="1"/>
+    <col min="5" max="5" width="22.8" customWidth="1"/>
+    <col min="7" max="7" width="58.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5173,7 +5346,7 @@
       </c>
     </row>
     <row r="122" spans="1:7">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="4" t="s">
         <v>277</v>
       </c>
       <c r="B122" s="3" t="s">
@@ -5196,7 +5369,7 @@
       </c>
     </row>
     <row r="123" spans="1:7">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="4" t="s">
         <v>279</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -5215,12 +5388,12 @@
         <v>231</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>227</v>
@@ -5229,7 +5402,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>11</v>
@@ -5238,12 +5411,12 @@
         <v>243</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>227</v>
@@ -5252,7 +5425,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>11</v>
@@ -5261,12 +5434,12 @@
         <v>243</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>227</v>
@@ -5275,7 +5448,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>11</v>
@@ -5284,12 +5457,12 @@
         <v>243</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>227</v>
@@ -5298,7 +5471,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>11</v>
@@ -5307,12 +5480,12 @@
         <v>243</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>34</v>
@@ -5321,21 +5494,21 @@
         <v>9</v>
       </c>
       <c r="D128" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>227</v>
@@ -5344,7 +5517,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>11</v>
@@ -5353,12 +5526,12 @@
         <v>243</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>241</v>
@@ -5367,7 +5540,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>11</v>
@@ -5376,12 +5549,12 @@
         <v>243</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>241</v>
@@ -5390,7 +5563,7 @@
         <v>9</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>11</v>
@@ -5399,12 +5572,12 @@
         <v>243</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>241</v>
@@ -5413,7 +5586,7 @@
         <v>9</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>11</v>
@@ -5422,12 +5595,12 @@
         <v>243</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>241</v>
@@ -5436,7 +5609,7 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>11</v>
@@ -5445,12 +5618,12 @@
         <v>243</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>227</v>
@@ -5459,7 +5632,7 @@
         <v>224</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>11</v>
@@ -5468,12 +5641,12 @@
         <v>243</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>227</v>
@@ -5482,7 +5655,7 @@
         <v>224</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>11</v>
@@ -5491,12 +5664,12 @@
         <v>231</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>34</v>
@@ -5505,7 +5678,7 @@
         <v>224</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>11</v>
@@ -5514,12 +5687,12 @@
         <v>231</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>227</v>
@@ -5528,7 +5701,7 @@
         <v>224</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>11</v>
@@ -5537,12 +5710,12 @@
         <v>231</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>227</v>
@@ -5551,7 +5724,7 @@
         <v>224</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>11</v>
@@ -5560,12 +5733,12 @@
         <v>231</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>227</v>
@@ -5574,7 +5747,7 @@
         <v>224</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>11</v>
@@ -5583,12 +5756,12 @@
         <v>231</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>227</v>
@@ -5597,7 +5770,7 @@
         <v>9</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>11</v>
@@ -5606,12 +5779,12 @@
         <v>243</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>8</v>
@@ -5620,21 +5793,21 @@
         <v>9</v>
       </c>
       <c r="D141" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>241</v>
@@ -5643,21 +5816,21 @@
         <v>9</v>
       </c>
       <c r="D142" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G142" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>227</v>
@@ -5666,21 +5839,21 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G143" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>227</v>
@@ -5689,21 +5862,21 @@
         <v>224</v>
       </c>
       <c r="D144" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>227</v>
@@ -5712,21 +5885,21 @@
         <v>9</v>
       </c>
       <c r="D145" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G145" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>34</v>
@@ -5735,21 +5908,21 @@
         <v>224</v>
       </c>
       <c r="D146" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>135</v>
@@ -5758,21 +5931,21 @@
         <v>22</v>
       </c>
       <c r="D147" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>227</v>
@@ -5781,7 +5954,7 @@
         <v>9</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>11</v>
@@ -5790,12 +5963,12 @@
         <v>231</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>241</v>
@@ -5804,7 +5977,7 @@
         <v>9</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>11</v>
@@ -5813,12 +5986,12 @@
         <v>243</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>227</v>
@@ -5827,21 +6000,21 @@
         <v>22</v>
       </c>
       <c r="D150" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>227</v>
@@ -5850,21 +6023,21 @@
         <v>22</v>
       </c>
       <c r="D151" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>241</v>
@@ -5873,21 +6046,21 @@
         <v>22</v>
       </c>
       <c r="D152" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="3" t="s">
         <v>338</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>227</v>
@@ -5896,7 +6069,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>11</v>
@@ -5905,12 +6078,12 @@
         <v>231</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:7">
-      <c r="A154" s="3" t="s">
-        <v>341</v>
+      <c r="A154" s="4" t="s">
+        <v>342</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>227</v>
@@ -5919,7 +6092,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>11</v>
@@ -5928,12 +6101,12 @@
         <v>243</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>227</v>
@@ -5942,21 +6115,21 @@
         <v>9</v>
       </c>
       <c r="D155" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>227</v>
@@ -5965,7 +6138,7 @@
         <v>9</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>24</v>
@@ -5974,12 +6147,12 @@
         <v>231</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>241</v>
@@ -5988,7 +6161,7 @@
         <v>9</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>11</v>
@@ -5997,12 +6170,12 @@
         <v>243</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>241</v>
@@ -6011,7 +6184,7 @@
         <v>9</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>11</v>
@@ -6020,12 +6193,12 @@
         <v>243</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>227</v>
@@ -6034,7 +6207,7 @@
         <v>9</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>11</v>
@@ -6043,12 +6216,12 @@
         <v>243</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>227</v>
@@ -6057,7 +6230,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>24</v>
@@ -6066,12 +6239,12 @@
         <v>231</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>227</v>
@@ -6080,7 +6253,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>24</v>
@@ -6089,12 +6262,12 @@
         <v>231</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>241</v>
@@ -6103,7 +6276,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>11</v>
@@ -6112,12 +6285,12 @@
         <v>243</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>241</v>
@@ -6126,7 +6299,7 @@
         <v>9</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>11</v>
@@ -6135,12 +6308,12 @@
         <v>243</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>241</v>
@@ -6149,7 +6322,7 @@
         <v>9</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>11</v>
@@ -6158,12 +6331,12 @@
         <v>243</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="165" spans="1:7">
-      <c r="A165" s="3" t="s">
-        <v>371</v>
+      <c r="A165" s="4" t="s">
+        <v>372</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>241</v>
@@ -6172,21 +6345,21 @@
         <v>9</v>
       </c>
       <c r="D165" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>227</v>
@@ -6195,7 +6368,7 @@
         <v>9</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>11</v>
@@ -6204,12 +6377,12 @@
         <v>231</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>241</v>
@@ -6218,23 +6391,227 @@
         <v>22</v>
       </c>
       <c r="D167" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="E167" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>375</v>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G167" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:G167">
-      <sortCondition ref="A2"/>
-    </sortState>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G176" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
